--- a/files/港岛-北角-君誉峰.xlsx
+++ b/files/港岛-北角-君誉峰.xlsx
@@ -8,7 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="君誉峰 销控表" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="君誉峰" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,7 +20,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="19">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -44,14 +44,19 @@
     </font>
     <font>
       <name val="Microsoft YaHei"/>
-      <color rgb="007F7F7F"/>
+      <b val="1"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00000000"/>
       <sz val="9"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
       <b val="1"/>
-      <color rgb="007F7F7F"/>
-      <sz val="11"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
@@ -63,7 +68,7 @@
       <name val="Microsoft YaHei"/>
       <b val="1"/>
       <color rgb="00004D00"/>
-      <sz val="11"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
@@ -74,7 +79,7 @@
       <name val="Microsoft YaHei"/>
       <b val="1"/>
       <color rgb="00002060"/>
-      <sz val="11"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
@@ -85,7 +90,7 @@
       <name val="Microsoft YaHei"/>
       <b val="1"/>
       <color rgb="00660000"/>
-      <sz val="11"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
@@ -95,9 +100,30 @@
     </font>
     <font>
       <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
       <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="11"/>
+      <color rgb="007F7F7F"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="8"/>
     </font>
   </fonts>
   <fills count="9">
@@ -145,8 +171,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E5E5E5"/>
-        <bgColor rgb="00E5E5E5"/>
+        <fgColor rgb="00E8E8E8"/>
+        <bgColor rgb="00E8E8E8"/>
       </patternFill>
     </fill>
   </fills>
@@ -176,7 +202,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -193,19 +219,7 @@
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -223,10 +237,34 @@
     <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -607,7 +645,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
@@ -13628,199 +13666,199 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:N27"/>
+  <dimension ref="A1:N26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
-    <col width="18" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
-    <col width="18" customWidth="1" min="13" max="13"/>
-    <col width="18" customWidth="1" min="14" max="14"/>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>君誉峰 - 君誉峰 销控网格图</t>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>君誉峰 销控网格图</t>
         </is>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>总套数</t>
         </is>
       </c>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="8" t="inlineStr">
         <is>
           <t>在售 (Sale)</t>
         </is>
       </c>
-      <c r="C2" s="8" t="inlineStr">
+      <c r="C2" s="9" t="inlineStr">
         <is>
           <t>已定价未售</t>
         </is>
       </c>
-      <c r="D2" s="9" t="inlineStr">
+      <c r="D2" s="10" t="inlineStr">
         <is>
           <t>已售 (Sold)</t>
         </is>
       </c>
-      <c r="E2" s="10" t="inlineStr">
+      <c r="E2" s="11" t="inlineStr">
         <is>
           <t>暂停销售</t>
         </is>
       </c>
-      <c r="F2" s="6" t="inlineStr">
+      <c r="F2" s="12" t="inlineStr">
         <is>
           <t>待售 (Pending)</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>281 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>9 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>272 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>281</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>272</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C4" s="19" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D4" s="19" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E4" s="19" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F4" s="19" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G4" s="19" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="H4" s="19" t="inlineStr">
         <is>
           <t>G</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="I4" s="19" t="inlineStr">
         <is>
           <t>H</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="J4" s="19" t="inlineStr">
         <is>
           <t>J</t>
         </is>
       </c>
-      <c r="K5" s="2" t="inlineStr">
+      <c r="K4" s="19" t="inlineStr">
         <is>
           <t>K</t>
         </is>
       </c>
-      <c r="L5" s="2" t="inlineStr">
+      <c r="L4" s="19" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="M5" s="2" t="inlineStr">
+      <c r="M4" s="19" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="N5" s="2" t="inlineStr">
+      <c r="N4" s="19" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>28/F</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr">
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
         <is>
           <t>A | 419呎 (2房)
-$1,928万
+$1928万
 $46,014/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C6" s="16" t="inlineStr">
+      <c r="C5" s="20" t="inlineStr">
         <is>
           <t>B | 248呎 (1房)
-$1,240万
+$1240万
 $50,000/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D6" s="16" t="inlineStr">
+      <c r="D5" s="20" t="inlineStr">
         <is>
           <t>C | 248呎 (1房)
-$1,250万
+$1250万
 $50,403/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E6" s="17" t="inlineStr">
+      <c r="E5" s="21" t="inlineStr">
         <is>
           <t>D | 418呎 (2房)
 招标单位
@@ -13828,7 +13866,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="F6" s="16" t="inlineStr">
+      <c r="F5" s="20" t="inlineStr">
         <is>
           <t>E | 230呎 (1房)
 $698万
@@ -13836,7 +13874,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G6" s="17" t="inlineStr">
+      <c r="G5" s="21" t="inlineStr">
         <is>
           <t>F | 355呎 (2房)
 招标单位
@@ -13844,7 +13882,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="H6" s="17" t="inlineStr">
+      <c r="H5" s="21" t="inlineStr">
         <is>
           <t>G | 355呎 (2房)
 招标单位
@@ -13852,7 +13890,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="I6" s="16" t="inlineStr">
+      <c r="I5" s="20" t="inlineStr">
         <is>
           <t>H | 230呎 (1房)
 $702万
@@ -13860,27 +13898,27 @@
 (已售)</t>
         </is>
       </c>
-      <c r="J6" s="18" t="inlineStr"/>
-      <c r="K6" s="18" t="inlineStr"/>
-      <c r="L6" s="18" t="inlineStr"/>
-      <c r="M6" s="18" t="inlineStr"/>
-      <c r="N6" s="18" t="inlineStr"/>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>27/F</t>
-        </is>
-      </c>
-      <c r="B7" s="16" t="inlineStr">
+      <c r="J5" s="22" t="inlineStr"/>
+      <c r="K5" s="22" t="inlineStr"/>
+      <c r="L5" s="22" t="inlineStr"/>
+      <c r="M5" s="22" t="inlineStr"/>
+      <c r="N5" s="22" t="inlineStr"/>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
         <is>
           <t>A | 365呎 (2房)
-$1,063万
+$1063万
 $29,113/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C7" s="16" t="inlineStr">
+      <c r="C6" s="20" t="inlineStr">
         <is>
           <t>B | 288呎 (1房)
 $838万
@@ -13888,7 +13926,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D7" s="16" t="inlineStr">
+      <c r="D6" s="20" t="inlineStr">
         <is>
           <t>C | 181呎 (开放式)
 $575万
@@ -13896,7 +13934,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E7" s="16" t="inlineStr">
+      <c r="E6" s="20" t="inlineStr">
         <is>
           <t>D | 205呎 (开放式)
 $620万
@@ -13904,7 +13942,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F7" s="17" t="inlineStr">
+      <c r="F6" s="21" t="inlineStr">
         <is>
           <t>E | 205呎 (开放式)
 $694万
@@ -13912,7 +13950,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="G7" s="16" t="inlineStr">
+      <c r="G6" s="20" t="inlineStr">
         <is>
           <t>F | 181呎 (开放式)
 $574万
@@ -13920,7 +13958,7 @@
 (21年-02月)</t>
         </is>
       </c>
-      <c r="H7" s="16" t="inlineStr">
+      <c r="H6" s="20" t="inlineStr">
         <is>
           <t>G | 287呎 (1房)
 $823万
@@ -13928,15 +13966,15 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I7" s="16" t="inlineStr">
+      <c r="I6" s="20" t="inlineStr">
         <is>
           <t>H | 365呎 (2房)
-$1,056万
+$1056万
 $28,922/呎
 (已售)</t>
         </is>
       </c>
-      <c r="J7" s="16" t="inlineStr">
+      <c r="J6" s="20" t="inlineStr">
         <is>
           <t>J | 258呎 (1房)
 $733万
@@ -13944,7 +13982,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="K7" s="16" t="inlineStr">
+      <c r="K6" s="20" t="inlineStr">
         <is>
           <t>K | 257呎 (1房)
 $762万
@@ -13952,7 +13990,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="L7" s="16" t="inlineStr">
+      <c r="L6" s="20" t="inlineStr">
         <is>
           <t>L | 250呎 (1房)
 $700万
@@ -13960,7 +13998,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="M7" s="16" t="inlineStr">
+      <c r="M6" s="20" t="inlineStr">
         <is>
           <t>M | 263呎 (1房)
 $777万
@@ -13968,7 +14006,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="N7" s="16" t="inlineStr">
+      <c r="N6" s="20" t="inlineStr">
         <is>
           <t>N | 258呎 (1房)
 $769万
@@ -13977,21 +14015,21 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>26/F</t>
-        </is>
-      </c>
-      <c r="B8" s="16" t="inlineStr">
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
         <is>
           <t>A | 365呎 (2房)
-$1,031万
+$1031万
 $28,240/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C8" s="16" t="inlineStr">
+      <c r="C7" s="20" t="inlineStr">
         <is>
           <t>B | 288呎 (1房)
 $815万
@@ -13999,7 +14037,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D8" s="16" t="inlineStr">
+      <c r="D7" s="20" t="inlineStr">
         <is>
           <t>C | 181呎 (开放式)
 $587万
@@ -14007,7 +14045,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E8" s="16" t="inlineStr">
+      <c r="E7" s="20" t="inlineStr">
         <is>
           <t>D | 205呎 (开放式)
 $607万
@@ -14015,7 +14053,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F8" s="17" t="inlineStr">
+      <c r="F7" s="21" t="inlineStr">
         <is>
           <t>E | 205呎 (开放式)
 $682万
@@ -14023,7 +14061,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="G8" s="16" t="inlineStr">
+      <c r="G7" s="20" t="inlineStr">
         <is>
           <t>F | 181呎 (开放式)
 $571万
@@ -14031,7 +14069,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H8" s="16" t="inlineStr">
+      <c r="H7" s="20" t="inlineStr">
         <is>
           <t>G | 288呎 (1房)
 $801万
@@ -14039,15 +14077,15 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I8" s="16" t="inlineStr">
+      <c r="I7" s="20" t="inlineStr">
         <is>
           <t>H | 365呎 (2房)
-$1,057万
+$1057万
 $28,948/呎
 (已售)</t>
         </is>
       </c>
-      <c r="J8" s="16" t="inlineStr">
+      <c r="J7" s="20" t="inlineStr">
         <is>
           <t>J | 258呎 (1房)
 $726万
@@ -14055,7 +14093,7 @@
 (20年-12月)</t>
         </is>
       </c>
-      <c r="K8" s="16" t="inlineStr">
+      <c r="K7" s="20" t="inlineStr">
         <is>
           <t>K | 257呎 (1房)
 $747万
@@ -14063,7 +14101,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="L8" s="16" t="inlineStr">
+      <c r="L7" s="20" t="inlineStr">
         <is>
           <t>L | 250呎 (1房)
 $694万
@@ -14071,7 +14109,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="M8" s="16" t="inlineStr">
+      <c r="M7" s="20" t="inlineStr">
         <is>
           <t>M | 263呎 (1房)
 $762万
@@ -14079,7 +14117,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="N8" s="16" t="inlineStr">
+      <c r="N7" s="20" t="inlineStr">
         <is>
           <t>N | 258呎 (1房)
 $761万
@@ -14088,21 +14126,21 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>25/F</t>
-        </is>
-      </c>
-      <c r="B9" s="16" t="inlineStr">
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B8" s="20" t="inlineStr">
         <is>
           <t>A | 365呎 (2房)
-$1,031万
+$1031万
 $28,252/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C9" s="16" t="inlineStr">
+      <c r="C8" s="20" t="inlineStr">
         <is>
           <t>B | 288呎 (1房)
 $799万
@@ -14110,7 +14148,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D9" s="16" t="inlineStr">
+      <c r="D8" s="20" t="inlineStr">
         <is>
           <t>C | 181呎 (开放式)
 $570万
@@ -14118,7 +14156,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E9" s="16" t="inlineStr">
+      <c r="E8" s="20" t="inlineStr">
         <is>
           <t>D | 205呎 (开放式)
 $608万
@@ -14126,7 +14164,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F9" s="17" t="inlineStr">
+      <c r="F8" s="21" t="inlineStr">
         <is>
           <t>E | 205呎 (开放式)
 $643万
@@ -14134,7 +14172,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="G9" s="16" t="inlineStr">
+      <c r="G8" s="20" t="inlineStr">
         <is>
           <t>F | 181呎 (开放式)
 $561万
@@ -14142,7 +14180,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H9" s="16" t="inlineStr">
+      <c r="H8" s="20" t="inlineStr">
         <is>
           <t>G | 288呎 (1房)
 $796万
@@ -14150,15 +14188,15 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I9" s="16" t="inlineStr">
+      <c r="I8" s="20" t="inlineStr">
         <is>
           <t>H | 365呎 (2房)
-$1,015万
+$1015万
 $27,806/呎
 (已售)</t>
         </is>
       </c>
-      <c r="J9" s="16" t="inlineStr">
+      <c r="J8" s="20" t="inlineStr">
         <is>
           <t>J | 258呎 (1房)
 $712万
@@ -14166,7 +14204,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="K9" s="16" t="inlineStr">
+      <c r="K8" s="20" t="inlineStr">
         <is>
           <t>K | 257呎 (1房)
 $740万
@@ -14174,7 +14212,7 @@
 (19年-06月)</t>
         </is>
       </c>
-      <c r="L9" s="16" t="inlineStr">
+      <c r="L8" s="20" t="inlineStr">
         <is>
           <t>L | 250呎 (1房)
 $701万
@@ -14182,7 +14220,7 @@
 (20年-05月)</t>
         </is>
       </c>
-      <c r="M9" s="16" t="inlineStr">
+      <c r="M8" s="20" t="inlineStr">
         <is>
           <t>M | 263呎 (1房)
 $754万
@@ -14190,7 +14228,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="N9" s="16" t="inlineStr">
+      <c r="N8" s="20" t="inlineStr">
         <is>
           <t>N | 258呎 (1房)
 $754万
@@ -14199,21 +14237,21 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>23/F</t>
-        </is>
-      </c>
-      <c r="B10" s="16" t="inlineStr">
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B9" s="20" t="inlineStr">
         <is>
           <t>A | 365呎 (2房)
-$1,010万
+$1010万
 $27,682/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C10" s="16" t="inlineStr">
+      <c r="C9" s="20" t="inlineStr">
         <is>
           <t>B | 288呎 (1房)
 $792万
@@ -14221,7 +14259,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D10" s="16" t="inlineStr">
+      <c r="D9" s="20" t="inlineStr">
         <is>
           <t>C | 181呎 (开放式)
 $541万
@@ -14229,7 +14267,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E10" s="16" t="inlineStr">
+      <c r="E9" s="20" t="inlineStr">
         <is>
           <t>D | 205呎 (开放式)
 $602万
@@ -14237,7 +14275,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F10" s="17" t="inlineStr">
+      <c r="F9" s="21" t="inlineStr">
         <is>
           <t>E | 205呎 (开放式)
 $639万
@@ -14245,7 +14283,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="G10" s="16" t="inlineStr">
+      <c r="G9" s="20" t="inlineStr">
         <is>
           <t>F | 181呎 (开放式)
 $552万
@@ -14253,7 +14291,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H10" s="16" t="inlineStr">
+      <c r="H9" s="20" t="inlineStr">
         <is>
           <t>G | 288呎 (1房)
 $791万
@@ -14261,15 +14299,15 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I10" s="16" t="inlineStr">
+      <c r="I9" s="20" t="inlineStr">
         <is>
           <t>H | 365呎 (2房)
-$1,015万
+$1015万
 $27,816/呎
 (已售)</t>
         </is>
       </c>
-      <c r="J10" s="16" t="inlineStr">
+      <c r="J9" s="20" t="inlineStr">
         <is>
           <t>J | 258呎 (1房)
 $705万
@@ -14277,7 +14315,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="K10" s="16" t="inlineStr">
+      <c r="K9" s="20" t="inlineStr">
         <is>
           <t>K | 257呎 (1房)
 $740万
@@ -14285,7 +14323,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="L10" s="16" t="inlineStr">
+      <c r="L9" s="20" t="inlineStr">
         <is>
           <t>L | 250呎 (1房)
 $694万
@@ -14293,7 +14331,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="M10" s="16" t="inlineStr">
+      <c r="M9" s="20" t="inlineStr">
         <is>
           <t>M | 263呎 (1房)
 $747万
@@ -14301,7 +14339,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="N10" s="16" t="inlineStr">
+      <c r="N9" s="20" t="inlineStr">
         <is>
           <t>N | 258呎 (1房)
 $747万
@@ -14310,21 +14348,21 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>22/F</t>
-        </is>
-      </c>
-      <c r="B11" s="16" t="inlineStr">
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B10" s="20" t="inlineStr">
         <is>
           <t>A | 365呎 (2房)
-$1,035万
+$1035万
 $28,355/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C11" s="16" t="inlineStr">
+      <c r="C10" s="20" t="inlineStr">
         <is>
           <t>B | 288呎 (1房)
 $778万
@@ -14332,7 +14370,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D11" s="16" t="inlineStr">
+      <c r="D10" s="20" t="inlineStr">
         <is>
           <t>C | 181呎 (开放式)
 $538万
@@ -14340,7 +14378,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E11" s="16" t="inlineStr">
+      <c r="E10" s="20" t="inlineStr">
         <is>
           <t>D | 205呎 (开放式)
 $598万
@@ -14348,7 +14386,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F11" s="17" t="inlineStr">
+      <c r="F10" s="21" t="inlineStr">
         <is>
           <t>E | 205呎 (开放式)
 $634万
@@ -14356,7 +14394,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="G11" s="16" t="inlineStr">
+      <c r="G10" s="20" t="inlineStr">
         <is>
           <t>F | 181呎 (开放式)
 $554万
@@ -14364,7 +14402,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H11" s="16" t="inlineStr">
+      <c r="H10" s="20" t="inlineStr">
         <is>
           <t>G | 288呎 (1房)
 $786万
@@ -14372,7 +14410,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I11" s="16" t="inlineStr">
+      <c r="I10" s="20" t="inlineStr">
         <is>
           <t>H | 365呎 (2房)
 $988万
@@ -14380,7 +14418,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="J11" s="16" t="inlineStr">
+      <c r="J10" s="20" t="inlineStr">
         <is>
           <t>J | 258呎 (1房)
 $715万
@@ -14388,7 +14426,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="K11" s="16" t="inlineStr">
+      <c r="K10" s="20" t="inlineStr">
         <is>
           <t>K | 257呎 (1房)
 $751万
@@ -14396,7 +14434,7 @@
 (20年-03月)</t>
         </is>
       </c>
-      <c r="L11" s="16" t="inlineStr">
+      <c r="L10" s="20" t="inlineStr">
         <is>
           <t>L | 250呎 (1房)
 $669万
@@ -14404,7 +14442,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="M11" s="16" t="inlineStr">
+      <c r="M10" s="20" t="inlineStr">
         <is>
           <t>M | 263呎 (1房)
 $742万
@@ -14412,7 +14450,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="N11" s="16" t="inlineStr">
+      <c r="N10" s="20" t="inlineStr">
         <is>
           <t>N | 258呎 (1房)
 $734万
@@ -14421,21 +14459,21 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>21/F</t>
-        </is>
-      </c>
-      <c r="B12" s="16" t="inlineStr">
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B11" s="20" t="inlineStr">
         <is>
           <t>A | 365呎 (2房)
-$1,007万
+$1007万
 $27,593/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C12" s="16" t="inlineStr">
+      <c r="C11" s="20" t="inlineStr">
         <is>
           <t>B | 288呎 (1房)
 $773万
@@ -14443,7 +14481,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D12" s="16" t="inlineStr">
+      <c r="D11" s="20" t="inlineStr">
         <is>
           <t>C | 181呎 (开放式)
 $556万
@@ -14451,7 +14489,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E12" s="16" t="inlineStr">
+      <c r="E11" s="20" t="inlineStr">
         <is>
           <t>D | 205呎 (开放式)
 $600万
@@ -14459,7 +14497,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F12" s="16" t="inlineStr">
+      <c r="F11" s="20" t="inlineStr">
         <is>
           <t>E | 205呎 (开放式)
 $605万
@@ -14467,7 +14505,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G12" s="16" t="inlineStr">
+      <c r="G11" s="20" t="inlineStr">
         <is>
           <t>F | 181呎 (开放式)
 $550万
@@ -14475,7 +14513,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H12" s="16" t="inlineStr">
+      <c r="H11" s="20" t="inlineStr">
         <is>
           <t>G | 288呎 (1房)
 $780万
@@ -14483,7 +14521,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I12" s="16" t="inlineStr">
+      <c r="I11" s="20" t="inlineStr">
         <is>
           <t>H | 365呎 (2房)
 $981万
@@ -14491,7 +14529,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="J12" s="16" t="inlineStr">
+      <c r="J11" s="20" t="inlineStr">
         <is>
           <t>J | 258呎 (1房)
 $696万
@@ -14499,7 +14537,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="K12" s="16" t="inlineStr">
+      <c r="K11" s="20" t="inlineStr">
         <is>
           <t>K | 257呎 (1房)
 $723万
@@ -14507,7 +14545,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="L12" s="16" t="inlineStr">
+      <c r="L11" s="20" t="inlineStr">
         <is>
           <t>L | 250呎 (1房)
 $671万
@@ -14515,7 +14553,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="M12" s="16" t="inlineStr">
+      <c r="M11" s="20" t="inlineStr">
         <is>
           <t>M | 263呎 (1房)
 $744万
@@ -14523,7 +14561,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="N12" s="16" t="inlineStr">
+      <c r="N11" s="20" t="inlineStr">
         <is>
           <t>N | 258呎 (1房)
 $737万
@@ -14532,13 +14570,13 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>20/F</t>
-        </is>
-      </c>
-      <c r="B13" s="16" t="inlineStr">
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B12" s="20" t="inlineStr">
         <is>
           <t>A | 365呎 (2房)
 $990万
@@ -14546,7 +14584,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C13" s="16" t="inlineStr">
+      <c r="C12" s="20" t="inlineStr">
         <is>
           <t>B | 287呎 (1房)
 $776万
@@ -14554,7 +14592,7 @@
 (21年-05月)</t>
         </is>
       </c>
-      <c r="D13" s="16" t="inlineStr">
+      <c r="D12" s="20" t="inlineStr">
         <is>
           <t>C | 181呎 (开放式)
 $552万
@@ -14562,7 +14600,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E13" s="16" t="inlineStr">
+      <c r="E12" s="20" t="inlineStr">
         <is>
           <t>D | 205呎 (开放式)
 $583万
@@ -14570,7 +14608,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F13" s="16" t="inlineStr">
+      <c r="F12" s="20" t="inlineStr">
         <is>
           <t>E | 205呎 (开放式)
 $601万
@@ -14578,7 +14616,7 @@
 (19年-05月)</t>
         </is>
       </c>
-      <c r="G13" s="16" t="inlineStr">
+      <c r="G12" s="20" t="inlineStr">
         <is>
           <t>F | 181呎 (开放式)
 $541万
@@ -14586,7 +14624,7 @@
 (19年-07月)</t>
         </is>
       </c>
-      <c r="H13" s="16" t="inlineStr">
+      <c r="H12" s="20" t="inlineStr">
         <is>
           <t>G | 287呎 (1房)
 $783万
@@ -14594,15 +14632,15 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I13" s="16" t="inlineStr">
+      <c r="I12" s="20" t="inlineStr">
         <is>
           <t>H | 365呎 (2房)
-$1,005万
+$1005万
 $27,541/呎
 (已售)</t>
         </is>
       </c>
-      <c r="J13" s="16" t="inlineStr">
+      <c r="J12" s="20" t="inlineStr">
         <is>
           <t>J | 258呎 (1房)
 $698万
@@ -14610,7 +14648,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="K13" s="16" t="inlineStr">
+      <c r="K12" s="20" t="inlineStr">
         <is>
           <t>K | 257呎 (1房)
 $718万
@@ -14618,7 +14656,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="L13" s="16" t="inlineStr">
+      <c r="L12" s="20" t="inlineStr">
         <is>
           <t>L | 250呎 (1房)
 $660万
@@ -14626,7 +14664,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="M13" s="16" t="inlineStr">
+      <c r="M12" s="20" t="inlineStr">
         <is>
           <t>M | 263呎 (1房)
 $739万
@@ -14634,7 +14672,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="N13" s="16" t="inlineStr">
+      <c r="N12" s="20" t="inlineStr">
         <is>
           <t>N | 258呎 (1房)
 $732万
@@ -14643,21 +14681,21 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>19/F</t>
-        </is>
-      </c>
-      <c r="B14" s="16" t="inlineStr">
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B13" s="20" t="inlineStr">
         <is>
           <t>A | 365呎 (2房)
-$1,004万
+$1004万
 $27,499/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C14" s="16" t="inlineStr">
+      <c r="C13" s="20" t="inlineStr">
         <is>
           <t>B | 287呎 (1房)
 $763万
@@ -14665,7 +14703,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D14" s="16" t="inlineStr">
+      <c r="D13" s="20" t="inlineStr">
         <is>
           <t>C | 181呎 (开放式)
 $532万
@@ -14673,7 +14711,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E14" s="16" t="inlineStr">
+      <c r="E13" s="20" t="inlineStr">
         <is>
           <t>D | 205呎 (开放式)
 $579万
@@ -14681,7 +14719,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F14" s="16" t="inlineStr">
+      <c r="F13" s="20" t="inlineStr">
         <is>
           <t>E | 205呎 (开放式)
 $603万
@@ -14689,7 +14727,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G14" s="16" t="inlineStr">
+      <c r="G13" s="20" t="inlineStr">
         <is>
           <t>F | 181呎 (开放式)
 $537万
@@ -14697,7 +14735,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H14" s="16" t="inlineStr">
+      <c r="H13" s="20" t="inlineStr">
         <is>
           <t>G | 287呎 (1房)
 $770万
@@ -14705,7 +14743,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I14" s="16" t="inlineStr">
+      <c r="I13" s="20" t="inlineStr">
         <is>
           <t>H | 365呎 (2房)
 $998万
@@ -14713,7 +14751,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="J14" s="16" t="inlineStr">
+      <c r="J13" s="20" t="inlineStr">
         <is>
           <t>J | 258呎 (1房)
 $694万
@@ -14721,7 +14759,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="K14" s="16" t="inlineStr">
+      <c r="K13" s="20" t="inlineStr">
         <is>
           <t>K | 257呎 (1房)
 $721万
@@ -14729,7 +14767,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="L14" s="16" t="inlineStr">
+      <c r="L13" s="20" t="inlineStr">
         <is>
           <t>L | 250呎 (1房)
 $655万
@@ -14737,7 +14775,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="M14" s="16" t="inlineStr">
+      <c r="M13" s="20" t="inlineStr">
         <is>
           <t>M | 263呎 (1房)
 $727万
@@ -14745,7 +14783,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="N14" s="16" t="inlineStr">
+      <c r="N13" s="20" t="inlineStr">
         <is>
           <t>N | 258呎 (1房)
 $727万
@@ -14754,13 +14792,13 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>18/F</t>
-        </is>
-      </c>
-      <c r="B15" s="16" t="inlineStr">
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B14" s="20" t="inlineStr">
         <is>
           <t>A | 365呎 (2房)
 $987万
@@ -14768,7 +14806,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C15" s="16" t="inlineStr">
+      <c r="C14" s="20" t="inlineStr">
         <is>
           <t>B | 287呎 (1房)
 $757万
@@ -14776,7 +14814,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D15" s="16" t="inlineStr">
+      <c r="D14" s="20" t="inlineStr">
         <is>
           <t>C | 181呎 (开放式)
 $528万
@@ -14784,7 +14822,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E15" s="16" t="inlineStr">
+      <c r="E14" s="20" t="inlineStr">
         <is>
           <t>D | 205呎 (开放式)
 $581万
@@ -14792,7 +14830,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F15" s="16" t="inlineStr">
+      <c r="F14" s="20" t="inlineStr">
         <is>
           <t>E | 205呎 (开放式)
 $599万
@@ -14800,7 +14838,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G15" s="16" t="inlineStr">
+      <c r="G14" s="20" t="inlineStr">
         <is>
           <t>F | 181呎 (开放式)
 $539万
@@ -14808,7 +14846,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H15" s="16" t="inlineStr">
+      <c r="H14" s="20" t="inlineStr">
         <is>
           <t>G | 288呎 (1房)
 $773万
@@ -14816,7 +14854,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I15" s="16" t="inlineStr">
+      <c r="I14" s="20" t="inlineStr">
         <is>
           <t>H | 365呎 (2房)
 $962万
@@ -14824,7 +14862,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="J15" s="16" t="inlineStr">
+      <c r="J14" s="20" t="inlineStr">
         <is>
           <t>J | 258呎 (1房)
 $682万
@@ -14832,7 +14870,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="K15" s="16" t="inlineStr">
+      <c r="K14" s="20" t="inlineStr">
         <is>
           <t>K | 257呎 (1房)
 $716万
@@ -14840,7 +14878,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="L15" s="16" t="inlineStr">
+      <c r="L14" s="20" t="inlineStr">
         <is>
           <t>L | 250呎 (1房)
 $658万
@@ -14848,7 +14886,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="M15" s="16" t="inlineStr">
+      <c r="M14" s="20" t="inlineStr">
         <is>
           <t>M | 263呎 (1房)
 $729万
@@ -14856,7 +14894,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="N15" s="16" t="inlineStr">
+      <c r="N14" s="20" t="inlineStr">
         <is>
           <t>N | 258呎 (1房)
 $722万
@@ -14865,13 +14903,13 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>17/F</t>
-        </is>
-      </c>
-      <c r="B16" s="16" t="inlineStr">
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B15" s="20" t="inlineStr">
         <is>
           <t>A | 365呎 (2房)
 $966万
@@ -14879,7 +14917,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C16" s="16" t="inlineStr">
+      <c r="C15" s="20" t="inlineStr">
         <is>
           <t>B | 288呎 (1房)
 $749万
@@ -14887,7 +14925,7 @@
 (21年-03月)</t>
         </is>
       </c>
-      <c r="D16" s="16" t="inlineStr">
+      <c r="D15" s="20" t="inlineStr">
         <is>
           <t>C | 181呎 (开放式)
 $518万
@@ -14895,7 +14933,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E16" s="16" t="inlineStr">
+      <c r="E15" s="20" t="inlineStr">
         <is>
           <t>D | 205呎 (开放式)
 $569万
@@ -14903,7 +14941,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F16" s="16" t="inlineStr">
+      <c r="F15" s="20" t="inlineStr">
         <is>
           <t>E | 205呎 (开放式)
 $593万
@@ -14911,7 +14949,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G16" s="16" t="inlineStr">
+      <c r="G15" s="20" t="inlineStr">
         <is>
           <t>F | 181呎 (开放式)
 $533万
@@ -14919,7 +14957,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H16" s="16" t="inlineStr">
+      <c r="H15" s="20" t="inlineStr">
         <is>
           <t>G | 288呎 (1房)
 $757万
@@ -14927,7 +14965,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I16" s="16" t="inlineStr">
+      <c r="I15" s="20" t="inlineStr">
         <is>
           <t>H | 365呎 (2房)
 $962万
@@ -14935,7 +14973,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="J16" s="16" t="inlineStr">
+      <c r="J15" s="20" t="inlineStr">
         <is>
           <t>J | 258呎 (1房)
 $682万
@@ -14943,7 +14981,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="K16" s="16" t="inlineStr">
+      <c r="K15" s="20" t="inlineStr">
         <is>
           <t>K | 257呎 (1房)
 $708万
@@ -14951,7 +14989,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="L16" s="16" t="inlineStr">
+      <c r="L15" s="20" t="inlineStr">
         <is>
           <t>L | 250呎 (1房)
 $644万
@@ -14959,7 +14997,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="M16" s="16" t="inlineStr">
+      <c r="M15" s="20" t="inlineStr">
         <is>
           <t>M | 263呎 (1房)
 $714万
@@ -14967,7 +15005,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="N16" s="16" t="inlineStr">
+      <c r="N15" s="20" t="inlineStr">
         <is>
           <t>N | 258呎 (1房)
 $715万
@@ -14976,13 +15014,13 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>16/F</t>
-        </is>
-      </c>
-      <c r="B17" s="16" t="inlineStr">
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B16" s="20" t="inlineStr">
         <is>
           <t>A | 365呎 (2房)
 $999万
@@ -14990,7 +15028,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C17" s="16" t="inlineStr">
+      <c r="C16" s="20" t="inlineStr">
         <is>
           <t>B | 288呎 (1房)
 $744万
@@ -14998,7 +15036,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D17" s="16" t="inlineStr">
+      <c r="D16" s="20" t="inlineStr">
         <is>
           <t>C | 181呎 (开放式)
 $514万
@@ -15006,7 +15044,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E17" s="16" t="inlineStr">
+      <c r="E16" s="20" t="inlineStr">
         <is>
           <t>D | 205呎 (开放式)
 $571万
@@ -15014,7 +15052,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F17" s="16" t="inlineStr">
+      <c r="F16" s="20" t="inlineStr">
         <is>
           <t>E | 205呎 (开放式)
 $595万
@@ -15022,7 +15060,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G17" s="16" t="inlineStr">
+      <c r="G16" s="20" t="inlineStr">
         <is>
           <t>F | 181呎 (开放式)
 $524万
@@ -15030,7 +15068,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H17" s="16" t="inlineStr">
+      <c r="H16" s="20" t="inlineStr">
         <is>
           <t>G | 288呎 (1房)
 $760万
@@ -15038,7 +15076,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I17" s="16" t="inlineStr">
+      <c r="I16" s="20" t="inlineStr">
         <is>
           <t>H | 365呎 (2房)
 $955万
@@ -15046,7 +15084,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="J17" s="16" t="inlineStr">
+      <c r="J16" s="20" t="inlineStr">
         <is>
           <t>J | 258呎 (1房)
 $691万
@@ -15054,7 +15092,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="K17" s="16" t="inlineStr">
+      <c r="K16" s="20" t="inlineStr">
         <is>
           <t>K | 257呎 (1房)
 $696万
@@ -15062,7 +15100,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="L17" s="16" t="inlineStr">
+      <c r="L16" s="20" t="inlineStr">
         <is>
           <t>L | 250呎 (1房)
 $646万
@@ -15070,7 +15108,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="M17" s="16" t="inlineStr">
+      <c r="M16" s="20" t="inlineStr">
         <is>
           <t>M | 263呎 (1房)
 $709万
@@ -15078,7 +15116,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="N17" s="16" t="inlineStr">
+      <c r="N16" s="20" t="inlineStr">
         <is>
           <t>N | 258呎 (1房)
 $717万
@@ -15087,13 +15125,13 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="65" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>15/F</t>
-        </is>
-      </c>
-      <c r="B18" s="16" t="inlineStr">
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B17" s="20" t="inlineStr">
         <is>
           <t>A | 365呎 (2房)
 $953万
@@ -15101,7 +15139,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C18" s="16" t="inlineStr">
+      <c r="C17" s="20" t="inlineStr">
         <is>
           <t>B | 288呎 (1房)
 $739万
@@ -15109,7 +15147,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D18" s="16" t="inlineStr">
+      <c r="D17" s="20" t="inlineStr">
         <is>
           <t>C | 181呎 (开放式)
 $515万
@@ -15117,7 +15155,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E18" s="16" t="inlineStr">
+      <c r="E17" s="20" t="inlineStr">
         <is>
           <t>D | 205呎 (开放式)
 $567万
@@ -15125,7 +15163,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F18" s="16" t="inlineStr">
+      <c r="F17" s="20" t="inlineStr">
         <is>
           <t>E | 205呎 (开放式)
 $578万
@@ -15133,7 +15171,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G18" s="16" t="inlineStr">
+      <c r="G17" s="20" t="inlineStr">
         <is>
           <t>F | 181呎 (开放式)
 $520万
@@ -15141,7 +15179,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H18" s="16" t="inlineStr">
+      <c r="H17" s="20" t="inlineStr">
         <is>
           <t>G | 288呎 (1房)
 $747万
@@ -15149,7 +15187,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I18" s="16" t="inlineStr">
+      <c r="I17" s="20" t="inlineStr">
         <is>
           <t>H | 365呎 (2房)
 $968万
@@ -15157,7 +15195,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="J18" s="16" t="inlineStr">
+      <c r="J17" s="20" t="inlineStr">
         <is>
           <t>J | 258呎 (1房)
 $686万
@@ -15165,7 +15203,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="K18" s="16" t="inlineStr">
+      <c r="K17" s="20" t="inlineStr">
         <is>
           <t>K | 257呎 (1房)
 $699万
@@ -15173,7 +15211,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="L18" s="16" t="inlineStr">
+      <c r="L17" s="20" t="inlineStr">
         <is>
           <t>L | 250呎 (1房)
 $648万
@@ -15181,7 +15219,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="M18" s="16" t="inlineStr">
+      <c r="M17" s="20" t="inlineStr">
         <is>
           <t>M | 263呎 (1房)
 $704万
@@ -15189,7 +15227,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="N18" s="16" t="inlineStr">
+      <c r="N17" s="20" t="inlineStr">
         <is>
           <t>N | 258呎 (1房)
 $698万
@@ -15198,13 +15236,13 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="65" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>12/F</t>
-        </is>
-      </c>
-      <c r="B19" s="16" t="inlineStr">
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B18" s="20" t="inlineStr">
         <is>
           <t>A | 365呎 (2房)
 $946万
@@ -15212,7 +15250,7 @@
 (19年-03月)</t>
         </is>
       </c>
-      <c r="C19" s="16" t="inlineStr">
+      <c r="C18" s="20" t="inlineStr">
         <is>
           <t>B | 287呎 (1房)
 $734万
@@ -15220,7 +15258,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D19" s="16" t="inlineStr">
+      <c r="D18" s="20" t="inlineStr">
         <is>
           <t>C | 181呎 (开放式)
 $512万
@@ -15228,7 +15266,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E19" s="16" t="inlineStr">
+      <c r="E18" s="20" t="inlineStr">
         <is>
           <t>D | 205呎 (开放式)
 $557万
@@ -15236,7 +15274,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F19" s="16" t="inlineStr">
+      <c r="F18" s="20" t="inlineStr">
         <is>
           <t>E | 205呎 (开放式)
 $580万
@@ -15244,7 +15282,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G19" s="16" t="inlineStr">
+      <c r="G18" s="20" t="inlineStr">
         <is>
           <t>F | 181呎 (开放式)
 $527万
@@ -15252,7 +15290,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H19" s="16" t="inlineStr">
+      <c r="H18" s="20" t="inlineStr">
         <is>
           <t>G | 288呎 (1房)
 $741万
@@ -15260,7 +15298,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I19" s="16" t="inlineStr">
+      <c r="I18" s="20" t="inlineStr">
         <is>
           <t>H | 365呎 (2房)
 $942万
@@ -15268,7 +15306,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="J19" s="16" t="inlineStr">
+      <c r="J18" s="20" t="inlineStr">
         <is>
           <t>J | 258呎 (1房)
 $661万
@@ -15276,7 +15314,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="K19" s="16" t="inlineStr">
+      <c r="K18" s="20" t="inlineStr">
         <is>
           <t>K | 257呎 (1房)
 $694万
@@ -15284,7 +15322,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="L19" s="16" t="inlineStr">
+      <c r="L18" s="20" t="inlineStr">
         <is>
           <t>L | 250呎 (1房)
 $637万
@@ -15292,7 +15330,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="M19" s="16" t="inlineStr">
+      <c r="M18" s="20" t="inlineStr">
         <is>
           <t>M | 263呎 (1房)
 $706万
@@ -15300,7 +15338,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="N19" s="16" t="inlineStr">
+      <c r="N18" s="20" t="inlineStr">
         <is>
           <t>N | 258呎 (1房)
 $700万
@@ -15309,13 +15347,13 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="65" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>11/F</t>
-        </is>
-      </c>
-      <c r="B20" s="16" t="inlineStr">
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B19" s="20" t="inlineStr">
         <is>
           <t>A | 365呎 (2房)
 $968万
@@ -15323,7 +15361,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C20" s="16" t="inlineStr">
+      <c r="C19" s="20" t="inlineStr">
         <is>
           <t>B | 288呎 (1房)
 $736万
@@ -15331,7 +15369,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D20" s="16" t="inlineStr">
+      <c r="D19" s="20" t="inlineStr">
         <is>
           <t>C | 181呎 (开放式)
 $503万
@@ -15339,7 +15377,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E20" s="16" t="inlineStr">
+      <c r="E19" s="20" t="inlineStr">
         <is>
           <t>D | 205呎 (开放式)
 $559万
@@ -15347,7 +15385,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F20" s="16" t="inlineStr">
+      <c r="F19" s="20" t="inlineStr">
         <is>
           <t>E | 205呎 (开放式)
 $574万
@@ -15355,7 +15393,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G20" s="16" t="inlineStr">
+      <c r="G19" s="20" t="inlineStr">
         <is>
           <t>F | 181呎 (开放式)
 $509万
@@ -15363,7 +15401,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H20" s="16" t="inlineStr">
+      <c r="H19" s="20" t="inlineStr">
         <is>
           <t>G | 287呎 (1房)
 $739万
@@ -15371,7 +15409,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I20" s="16" t="inlineStr">
+      <c r="I19" s="20" t="inlineStr">
         <is>
           <t>H | 365呎 (2房)
 $935万
@@ -15379,7 +15417,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="J20" s="16" t="inlineStr">
+      <c r="J19" s="20" t="inlineStr">
         <is>
           <t>J | 258呎 (1房)
 $663万
@@ -15387,7 +15425,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="K20" s="16" t="inlineStr">
+      <c r="K19" s="20" t="inlineStr">
         <is>
           <t>K | 257呎 (1房)
 $682万
@@ -15395,7 +15433,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="L20" s="16" t="inlineStr">
+      <c r="L19" s="20" t="inlineStr">
         <is>
           <t>L | 250呎 (1房)
 $646万
@@ -15403,7 +15441,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="M20" s="16" t="inlineStr">
+      <c r="M19" s="20" t="inlineStr">
         <is>
           <t>M | 263呎 (1房)
 $701万
@@ -15411,7 +15449,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="N20" s="16" t="inlineStr">
+      <c r="N19" s="20" t="inlineStr">
         <is>
           <t>N | 258呎 (1房)
 $695万
@@ -15420,13 +15458,13 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="65" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>10/F</t>
-        </is>
-      </c>
-      <c r="B21" s="16" t="inlineStr">
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B20" s="20" t="inlineStr">
         <is>
           <t>A | 365呎 (2房)
 $971万
@@ -15434,7 +15472,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C21" s="16" t="inlineStr">
+      <c r="C20" s="20" t="inlineStr">
         <is>
           <t>B | 288呎 (1房)
 $723万
@@ -15442,7 +15480,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D21" s="16" t="inlineStr">
+      <c r="D20" s="20" t="inlineStr">
         <is>
           <t>C | 181呎 (开放式)
 $504万
@@ -15450,7 +15488,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E21" s="16" t="inlineStr">
+      <c r="E20" s="20" t="inlineStr">
         <is>
           <t>D | 205呎 (开放式)
 $555万
@@ -15458,7 +15496,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F21" s="16" t="inlineStr">
+      <c r="F20" s="20" t="inlineStr">
         <is>
           <t>E | 205呎 (开放式)
 $574万
@@ -15466,7 +15504,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G21" s="16" t="inlineStr">
+      <c r="G20" s="20" t="inlineStr">
         <is>
           <t>F | 181呎 (开放式)
 $512万
@@ -15474,7 +15512,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H21" s="16" t="inlineStr">
+      <c r="H20" s="20" t="inlineStr">
         <is>
           <t>G | 288呎 (1房)
 $721万
@@ -15482,7 +15520,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I21" s="16" t="inlineStr">
+      <c r="I20" s="20" t="inlineStr">
         <is>
           <t>H | 365呎 (2房)
 $938万
@@ -15490,7 +15528,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="J21" s="16" t="inlineStr">
+      <c r="J20" s="20" t="inlineStr">
         <is>
           <t>J | 258呎 (1房)
 $658万
@@ -15498,7 +15536,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="K21" s="16" t="inlineStr">
+      <c r="K20" s="20" t="inlineStr">
         <is>
           <t>K | 257呎 (1房)
 $684万
@@ -15506,7 +15544,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="L21" s="16" t="inlineStr">
+      <c r="L20" s="20" t="inlineStr">
         <is>
           <t>L | 250呎 (1房)
 $622万
@@ -15514,7 +15552,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="M21" s="16" t="inlineStr">
+      <c r="M20" s="20" t="inlineStr">
         <is>
           <t>M | 263呎 (1房)
 $696万
@@ -15522,7 +15560,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="N21" s="16" t="inlineStr">
+      <c r="N20" s="20" t="inlineStr">
         <is>
           <t>N | 258呎 (1房)
 $690万
@@ -15531,13 +15569,13 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="65" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>9/F</t>
-        </is>
-      </c>
-      <c r="B22" s="16" t="inlineStr">
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B21" s="20" t="inlineStr">
         <is>
           <t>A | 365呎 (2房)
 $935万
@@ -15545,7 +15583,7 @@
 (18年-06月)</t>
         </is>
       </c>
-      <c r="C22" s="16" t="inlineStr">
+      <c r="C21" s="20" t="inlineStr">
         <is>
           <t>B | 287呎 (1房)
 $718万
@@ -15553,7 +15591,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D22" s="16" t="inlineStr">
+      <c r="D21" s="20" t="inlineStr">
         <is>
           <t>C | 181呎 (开放式)
 $501万
@@ -15561,7 +15599,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E22" s="16" t="inlineStr">
+      <c r="E21" s="20" t="inlineStr">
         <is>
           <t>D | 205呎 (开放式)
 $556万
@@ -15569,7 +15607,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F22" s="16" t="inlineStr">
+      <c r="F21" s="20" t="inlineStr">
         <is>
           <t>E | 205呎 (开放式)
 $575万
@@ -15577,7 +15615,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G22" s="16" t="inlineStr">
+      <c r="G21" s="20" t="inlineStr">
         <is>
           <t>F | 181呎 (开放式)
 $504万
@@ -15585,7 +15623,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H22" s="16" t="inlineStr">
+      <c r="H21" s="20" t="inlineStr">
         <is>
           <t>G | 288呎 (1房)
 $723万
@@ -15593,7 +15631,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I22" s="16" t="inlineStr">
+      <c r="I21" s="20" t="inlineStr">
         <is>
           <t>H | 365呎 (2房)
 $922万
@@ -15601,7 +15639,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="J22" s="16" t="inlineStr">
+      <c r="J21" s="20" t="inlineStr">
         <is>
           <t>J | 258呎 (1房)
 $654万
@@ -15609,7 +15647,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="K22" s="16" t="inlineStr">
+      <c r="K21" s="20" t="inlineStr">
         <is>
           <t>K | 257呎 (1房)
 $672万
@@ -15617,7 +15655,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="L22" s="16" t="inlineStr">
+      <c r="L21" s="20" t="inlineStr">
         <is>
           <t>L | 250呎 (1房)
 $617万
@@ -15625,7 +15663,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="M22" s="16" t="inlineStr">
+      <c r="M21" s="20" t="inlineStr">
         <is>
           <t>M | 263呎 (1房)
 $691万
@@ -15633,7 +15671,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="N22" s="16" t="inlineStr">
+      <c r="N21" s="20" t="inlineStr">
         <is>
           <t>N | 258呎 (1房)
 $685万
@@ -15642,13 +15680,13 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="65" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>8/F</t>
-        </is>
-      </c>
-      <c r="B23" s="16" t="inlineStr">
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B22" s="20" t="inlineStr">
         <is>
           <t>A | 365呎 (2房)
 $951万
@@ -15656,7 +15694,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C23" s="16" t="inlineStr">
+      <c r="C22" s="20" t="inlineStr">
         <is>
           <t>B | 288呎 (1房)
 $716万
@@ -15664,7 +15702,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D23" s="16" t="inlineStr">
+      <c r="D22" s="20" t="inlineStr">
         <is>
           <t>C | 181呎 (开放式)
 $494万
@@ -15672,7 +15710,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E23" s="16" t="inlineStr">
+      <c r="E22" s="20" t="inlineStr">
         <is>
           <t>D | 205呎 (开放式)
 $554万
@@ -15680,7 +15718,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F23" s="16" t="inlineStr">
+      <c r="F22" s="20" t="inlineStr">
         <is>
           <t>E | 205呎 (开放式)
 $556万
@@ -15688,7 +15726,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G23" s="16" t="inlineStr">
+      <c r="G22" s="20" t="inlineStr">
         <is>
           <t>F | 181呎 (开放式)
 $496万
@@ -15696,7 +15734,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H23" s="16" t="inlineStr">
+      <c r="H22" s="20" t="inlineStr">
         <is>
           <t>G | 288呎 (1房)
 $713万
@@ -15704,7 +15742,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I23" s="16" t="inlineStr">
+      <c r="I22" s="20" t="inlineStr">
         <is>
           <t>H | 365呎 (2房)
 $918万
@@ -15712,7 +15750,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="J23" s="16" t="inlineStr">
+      <c r="J22" s="20" t="inlineStr">
         <is>
           <t>J | 258呎 (1房)
 $658万
@@ -15720,7 +15758,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="K23" s="16" t="inlineStr">
+      <c r="K22" s="20" t="inlineStr">
         <is>
           <t>K | 257呎 (1房)
 $677万
@@ -15728,7 +15766,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="L23" s="16" t="inlineStr">
+      <c r="L22" s="20" t="inlineStr">
         <is>
           <t>L | 250呎 (1房)
 $621万
@@ -15736,7 +15774,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="M23" s="16" t="inlineStr">
+      <c r="M22" s="20" t="inlineStr">
         <is>
           <t>M | 263呎 (1房)
 $688万
@@ -15744,7 +15782,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="N23" s="16" t="inlineStr">
+      <c r="N22" s="20" t="inlineStr">
         <is>
           <t>N | 258呎 (1房)
 $697万
@@ -15753,13 +15791,13 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="65" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>7/F</t>
-        </is>
-      </c>
-      <c r="B24" s="16" t="inlineStr">
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B23" s="20" t="inlineStr">
         <is>
           <t>A | 365呎 (2房)
 $925万
@@ -15767,7 +15805,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C24" s="16" t="inlineStr">
+      <c r="C23" s="20" t="inlineStr">
         <is>
           <t>B | 287呎 (1房)
 $710万
@@ -15775,7 +15813,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D24" s="16" t="inlineStr">
+      <c r="D23" s="20" t="inlineStr">
         <is>
           <t>C | 181呎 (开放式)
 $505万
@@ -15783,7 +15821,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E24" s="16" t="inlineStr">
+      <c r="E23" s="20" t="inlineStr">
         <is>
           <t>D | 205呎 (开放式)
 $545万
@@ -15791,7 +15829,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F24" s="16" t="inlineStr">
+      <c r="F23" s="20" t="inlineStr">
         <is>
           <t>E | 205呎 (开放式)
 $563万
@@ -15799,7 +15837,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G24" s="16" t="inlineStr">
+      <c r="G23" s="20" t="inlineStr">
         <is>
           <t>F | 181呎 (开放式)
 $480万
@@ -15807,7 +15845,7 @@
 (19年-06月)</t>
         </is>
       </c>
-      <c r="H24" s="16" t="inlineStr">
+      <c r="H23" s="20" t="inlineStr">
         <is>
           <t>G | 288呎 (1房)
 $708万
@@ -15815,7 +15853,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I24" s="16" t="inlineStr">
+      <c r="I23" s="20" t="inlineStr">
         <is>
           <t>H | 365呎 (2房)
 $912万
@@ -15823,7 +15861,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="J24" s="16" t="inlineStr">
+      <c r="J23" s="20" t="inlineStr">
         <is>
           <t>J | 258呎 (1房)
 $640万
@@ -15831,7 +15869,7 @@
 (20年-02月)</t>
         </is>
       </c>
-      <c r="K24" s="16" t="inlineStr">
+      <c r="K23" s="20" t="inlineStr">
         <is>
           <t>K | 257呎 (1房)
 $672万
@@ -15839,7 +15877,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="L24" s="16" t="inlineStr">
+      <c r="L23" s="20" t="inlineStr">
         <is>
           <t>L | 250呎 (1房)
 $630万
@@ -15847,7 +15885,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="M24" s="16" t="inlineStr">
+      <c r="M23" s="20" t="inlineStr">
         <is>
           <t>M | 263呎 (1房)
 $697万
@@ -15855,7 +15893,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="N24" s="16" t="inlineStr">
+      <c r="N23" s="20" t="inlineStr">
         <is>
           <t>N | 258呎 (1房)
 $699万
@@ -15864,13 +15902,13 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="65" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>6/F</t>
-        </is>
-      </c>
-      <c r="B25" s="16" t="inlineStr">
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B24" s="20" t="inlineStr">
         <is>
           <t>A | 365呎 (2房)
 $909万
@@ -15878,7 +15916,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C25" s="16" t="inlineStr">
+      <c r="C24" s="20" t="inlineStr">
         <is>
           <t>B | 288呎 (1房)
 $705万
@@ -15886,7 +15924,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D25" s="16" t="inlineStr">
+      <c r="D24" s="20" t="inlineStr">
         <is>
           <t>C | 181呎 (开放式)
 $504万
@@ -15894,7 +15932,7 @@
 (18年-01月)</t>
         </is>
       </c>
-      <c r="E25" s="16" t="inlineStr">
+      <c r="E24" s="20" t="inlineStr">
         <is>
           <t>D | 205呎 (开放式)
 $538万
@@ -15902,7 +15940,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F25" s="16" t="inlineStr">
+      <c r="F24" s="20" t="inlineStr">
         <is>
           <t>E | 205呎 (开放式)
 $546万
@@ -15910,7 +15948,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G25" s="16" t="inlineStr">
+      <c r="G24" s="20" t="inlineStr">
         <is>
           <t>F | 181呎 (开放式)
 $497万
@@ -15918,7 +15956,7 @@
 (19年-06月)</t>
         </is>
       </c>
-      <c r="H25" s="16" t="inlineStr">
+      <c r="H24" s="20" t="inlineStr">
         <is>
           <t>G | 287呎 (1房)
 $702万
@@ -15926,7 +15964,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I25" s="16" t="inlineStr">
+      <c r="I24" s="20" t="inlineStr">
         <is>
           <t>H | 365呎 (2房)
 $914万
@@ -15934,7 +15972,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="J25" s="16" t="inlineStr">
+      <c r="J24" s="20" t="inlineStr">
         <is>
           <t>J | 258呎 (1房)
 $635万
@@ -15942,7 +15980,7 @@
 (19年-12月)</t>
         </is>
       </c>
-      <c r="K25" s="16" t="inlineStr">
+      <c r="K24" s="20" t="inlineStr">
         <is>
           <t>K | 257呎 (1房)
 $660万
@@ -15950,7 +15988,7 @@
 (19年-05月)</t>
         </is>
       </c>
-      <c r="L25" s="16" t="inlineStr">
+      <c r="L24" s="20" t="inlineStr">
         <is>
           <t>L | 250呎 (1房)
 $612万
@@ -15958,7 +15996,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="M25" s="16" t="inlineStr">
+      <c r="M24" s="20" t="inlineStr">
         <is>
           <t>M | 263呎 (1房)
 $678万
@@ -15966,7 +16004,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="N25" s="16" t="inlineStr">
+      <c r="N24" s="20" t="inlineStr">
         <is>
           <t>N | 258呎 (1房)
 $694万
@@ -15975,13 +16013,13 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="65" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>5/F</t>
-        </is>
-      </c>
-      <c r="B26" s="16" t="inlineStr">
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B25" s="20" t="inlineStr">
         <is>
           <t>A | 365呎 (2房)
 $902万
@@ -15989,7 +16027,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C26" s="16" t="inlineStr">
+      <c r="C25" s="20" t="inlineStr">
         <is>
           <t>B | 287呎 (1房)
 $697万
@@ -15997,7 +16035,7 @@
 (21年-02月)</t>
         </is>
       </c>
-      <c r="D26" s="16" t="inlineStr">
+      <c r="D25" s="20" t="inlineStr">
         <is>
           <t>C | 181呎 (开放式)
 $477万
@@ -16005,7 +16043,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E26" s="16" t="inlineStr">
+      <c r="E25" s="20" t="inlineStr">
         <is>
           <t>D | 205呎 (开放式)
 $530万
@@ -16013,7 +16051,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F26" s="16" t="inlineStr">
+      <c r="F25" s="20" t="inlineStr">
         <is>
           <t>E | 205呎 (开放式)
 $549万
@@ -16021,7 +16059,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G26" s="16" t="inlineStr">
+      <c r="G25" s="20" t="inlineStr">
         <is>
           <t>F | 181呎 (开放式)
 $480万
@@ -16029,7 +16067,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H26" s="16" t="inlineStr">
+      <c r="H25" s="20" t="inlineStr">
         <is>
           <t>G | 288呎 (1房)
 $704万
@@ -16037,7 +16075,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I26" s="16" t="inlineStr">
+      <c r="I25" s="20" t="inlineStr">
         <is>
           <t>H | 365呎 (2房)
 $898万
@@ -16045,7 +16083,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="J26" s="16" t="inlineStr">
+      <c r="J25" s="20" t="inlineStr">
         <is>
           <t>J | 258呎 (1房)
 $657万
@@ -16053,7 +16091,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="K26" s="16" t="inlineStr">
+      <c r="K25" s="20" t="inlineStr">
         <is>
           <t>K | 257呎 (1房)
 $662万
@@ -16061,7 +16099,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="L26" s="16" t="inlineStr">
+      <c r="L25" s="20" t="inlineStr">
         <is>
           <t>L | 250呎 (1房)
 $608万
@@ -16069,7 +16107,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="M26" s="16" t="inlineStr">
+      <c r="M25" s="20" t="inlineStr">
         <is>
           <t>M | 263呎 (1房)
 $666万
@@ -16077,7 +16115,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="N26" s="16" t="inlineStr">
+      <c r="N25" s="20" t="inlineStr">
         <is>
           <t>N | 258呎 (1房)
 $661万
@@ -16086,21 +16124,21 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="65" customHeight="1">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>3/F</t>
-        </is>
-      </c>
-      <c r="B27" s="16" t="inlineStr">
+    <row r="26" ht="58" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B26" s="20" t="inlineStr">
         <is>
           <t>A | 352呎 (2房)
-$1,001万
+$1001万
 $28,432/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C27" s="16" t="inlineStr">
+      <c r="C26" s="20" t="inlineStr">
         <is>
           <t>B | 287呎 (1房)
 $834万
@@ -16108,7 +16146,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D27" s="16" t="inlineStr">
+      <c r="D26" s="20" t="inlineStr">
         <is>
           <t>C | 181呎 (开放式)
 $470万
@@ -16116,7 +16154,7 @@
 (21年-02月)</t>
         </is>
       </c>
-      <c r="E27" s="16" t="inlineStr">
+      <c r="E26" s="20" t="inlineStr">
         <is>
           <t>D | 205呎 (开放式)
 $522万
@@ -16124,7 +16162,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F27" s="16" t="inlineStr">
+      <c r="F26" s="20" t="inlineStr">
         <is>
           <t>E | 205呎 (开放式)
 $530万
@@ -16132,7 +16170,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G27" s="16" t="inlineStr">
+      <c r="G26" s="20" t="inlineStr">
         <is>
           <t>F | 181呎 (开放式)
 $487万
@@ -16140,7 +16178,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H27" s="16" t="inlineStr">
+      <c r="H26" s="20" t="inlineStr">
         <is>
           <t>G | 287呎 (1房)
 $834万
@@ -16148,7 +16186,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I27" s="17" t="inlineStr">
+      <c r="I26" s="21" t="inlineStr">
         <is>
           <t>H | 352呎 (2房)
 招标单位
@@ -16156,7 +16194,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="J27" s="16" t="inlineStr">
+      <c r="J26" s="20" t="inlineStr">
         <is>
           <t>J | 258呎 (1房)
 $643万
@@ -16164,7 +16202,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="K27" s="16" t="inlineStr">
+      <c r="K26" s="20" t="inlineStr">
         <is>
           <t>K | 257呎 (1房)
 $655万
@@ -16172,7 +16210,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="L27" s="16" t="inlineStr">
+      <c r="L26" s="20" t="inlineStr">
         <is>
           <t>L | 250呎 (1房)
 $595万
@@ -16180,7 +16218,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="M27" s="16" t="inlineStr">
+      <c r="M26" s="20" t="inlineStr">
         <is>
           <t>M | 263呎 (1房)
 $665万
@@ -16188,7 +16226,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="N27" s="16" t="inlineStr">
+      <c r="N26" s="20" t="inlineStr">
         <is>
           <t>N | 258呎 (1房)
 $654万
@@ -16199,7 +16237,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:N1"/>
+    <mergeCell ref="A1:F1"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
